--- a/Documentação/Matriz de perguntas.xlsx
+++ b/Documentação/Matriz de perguntas.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/35ffef9519f1216b/Faculdade/Semestre 4/Analise de dados/BI/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\SPTech\REPOSITÓRIOS LAMAR\AnaliseDados_Grupo7\Documentação\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="88" documentId="11_F25DC773A252ABDACC1048B329DD671C5BDE58E6" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E9607C31-7813-48FB-B321-A42062E9AA99}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C695C89B-590C-4CEF-9099-347F357A75B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="14616" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Perguntas vFinal" sheetId="2" r:id="rId1"/>
+    <sheet name="Perguntas v1" sheetId="1" r:id="rId2"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -25,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="48" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="125">
   <si>
     <t>Pergunta</t>
   </si>
@@ -78,9 +79,6 @@
     <t>Valor total da importação/ano e categoria</t>
   </si>
   <si>
-    <t>Qual o mês da analise</t>
-  </si>
-  <si>
     <t>split, np</t>
   </si>
   <si>
@@ -111,9 +109,6 @@
     <t>Qual o peso da produção das peças em quilos</t>
   </si>
   <si>
-    <t>Qual a categoria de cada  gurpo de codigo NCM</t>
-  </si>
-  <si>
     <t>Descrição NCM</t>
   </si>
   <si>
@@ -130,19 +125,1582 @@
   </si>
   <si>
     <t>Valor e porcentagem de importação por categoria e país de origem por ano</t>
+  </si>
+  <si>
+    <t>Qual o mês da análise</t>
+  </si>
+  <si>
+    <t>Qual a categoria de cada  gurpo de código NCM</t>
+  </si>
+  <si>
+    <t>Pergunta vaga</t>
+  </si>
+  <si>
+    <t>Colunas necessárias</t>
+  </si>
+  <si>
+    <t>Tem na base?</t>
+  </si>
+  <si>
+    <t>Predomina o valor do mercado de empilhadeiras: produção nacional ou importação?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Em toda a série histórica, o valor em dólar da produção nacional ou das importações foi maior? Como essa diferença se comporta quando analisamos separadamente </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>peças</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>empilhadeiras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Valor total por ano, origem e categoria</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Origem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor (USD)</t>
+    </r>
+  </si>
+  <si>
+    <t>groupby + agg + sum + merge</t>
+  </si>
+  <si>
+    <t>Em quantidade absoluta, temos mais peças nacionais ou importadas?</t>
+  </si>
+  <si>
+    <t>Em toda a série histórica, foi produzido um volume maior de peças no Brasil ou foi importado um volume maior? Como essa diferença evoluiu ao longo dos anos?</t>
+  </si>
+  <si>
+    <t>Volume/peso total por ano, origem e categoria</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Origem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Unidade</t>
+    </r>
+  </si>
+  <si>
+    <t>Em quantidade absoluta, temos mais empilhadeiras nacionais ou importadas?</t>
+  </si>
+  <si>
+    <t>Em toda a série histórica, foram produzidas mais empilhadeiras no Brasil ou foram importadas mais unidades? Como essa diferença evoluiu ao longo dos anos?</t>
+  </si>
+  <si>
+    <t>Quantidade total de unidades por ano, origem e categoria</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Origem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+  </si>
+  <si>
+    <t>Qual é a participação das importações no mercado?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo da série histórica, qual percentual do valor total do mercado de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>empilhadeiras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> corresponde às importações e qual percentual corresponde à produção nacional? E como essa participação evoluiu ano a ano?</t>
+    </r>
+  </si>
+  <si>
+    <t>Participação percentual por origem</t>
+  </si>
+  <si>
+    <t>groupby + sum + merge + divisão</t>
+  </si>
+  <si>
+    <t>Qual é a participação das importações em peças?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo da série histórica, qual percentual do valor total de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>peças</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> corresponde às importações e qual corresponde à produção nacional?</t>
+    </r>
+  </si>
+  <si>
+    <t>O mercado de empilhadeiras está crescendo?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como o mercado de empilhadeiras evoluiu ao longo da série histórica em </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valor e quantidade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>? Houve crescimento ou redução ao longo dos anos?</t>
+    </r>
+  </si>
+  <si>
+    <t>Crescimento anual (%) de valor e quantidade</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+  </si>
+  <si>
+    <t>groupby + sum + pct_change</t>
+  </si>
+  <si>
+    <t>O mercado de peças está crescendo?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como o mercado de peças evoluiu ao longo da série histórica em </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valor e volume/peso</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Crescimento anual (%) de valor e volume</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Unidade</t>
+    </r>
+  </si>
+  <si>
+    <t>Quais países mais exportam empilhadeiras para o Brasil?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo de toda a série histórica, quais países foram responsáveis pelo maior volume de importações de empilhadeiras para o Brasil, considerando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quantidade e valor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Valor total e quantidade total por país</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>País</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor US$ FOB</t>
+    </r>
+  </si>
+  <si>
+    <t>groupby + agg + sum + sort_values</t>
+  </si>
+  <si>
+    <t>Quais países mais exportam peças para o Brasil?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo de toda a série histórica, quais países foram responsáveis pelo maior volume de importações de peças para o Brasil, considerando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>peso/quantidade e valor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Valor total e volume total por país</t>
+  </si>
+  <si>
+    <t>De quais países o Brasil mais depende para empilhadeiras?</t>
+  </si>
+  <si>
+    <t>Qual foi a participação de cada país no total das importações brasileiras de empilhadeiras ao longo da série histórica?</t>
+  </si>
+  <si>
+    <t>Participação (%) das importações por país</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>País</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor US$ FOB</t>
+    </r>
+  </si>
+  <si>
+    <t>groupby + sum + transform('sum') + divisão</t>
+  </si>
+  <si>
+    <t>De quais países o Brasil mais depende para peças?</t>
+  </si>
+  <si>
+    <t>Qual foi a participação de cada país no total das importações brasileiras de peças ao longo da série histórica?</t>
+  </si>
+  <si>
+    <t>Quais estados concentram o mercado de empilhadeiras?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo da série histórica, quais estados/UFs apresentaram o maior volume de empilhadeiras, considerando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quantidade e valor das importações</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantidade e valor por UF</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>UF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor US$ FOB</t>
+    </r>
+  </si>
+  <si>
+    <t>Quais estados concentram o mercado de peças?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo da série histórica, quais estados/UFs apresentaram o maior volume de peças, considerando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>peso e valor das importações</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Peso e valor por UF</t>
+  </si>
+  <si>
+    <t>O mercado está concentrado em poucos estados?</t>
+  </si>
+  <si>
+    <t>Qual percentual das importações de empilhadeiras e peças está concentrado nos principais estados/UFs?</t>
+  </si>
+  <si>
+    <t>Participação (%) por UF</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>UF</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor US$ FOB</t>
+    </r>
+  </si>
+  <si>
+    <t>Quais meses têm maior movimento no mercado de empilhadeiras?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo da série histórica, quais meses apresentam o maior volume de produção e importação de empilhadeiras, considerando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>quantidade e valor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Quantidade e valor por mês</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Mês</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Origem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor</t>
+    </r>
+  </si>
+  <si>
+    <t>Quais meses têm maior movimento no mercado de peças?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo da série histórica, quais meses apresentam o maior volume de produção e importação de peças, considerando </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>volume/peso e valor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>?</t>
+    </r>
+  </si>
+  <si>
+    <t>Volume/peso e valor por mês</t>
+  </si>
+  <si>
+    <t>Existe sazonalidade no mercado?</t>
+  </si>
+  <si>
+    <t>Existe um padrão sazonal nas vendas/produção/importações de empilhadeiras e peças? Quais meses concentram os maiores e menores volumes?</t>
+  </si>
+  <si>
+    <t>Média mensal e índice sazonal</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Mês</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor</t>
+    </r>
+  </si>
+  <si>
+    <t>groupby + mean + pivot_table</t>
+  </si>
+  <si>
+    <t>O valor médio das empilhadeiras está aumentando?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como evoluiu o </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valor médio por empilhadeira</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ao longo da série histórica, comparando produção nacional e importações?</t>
+    </r>
+  </si>
+  <si>
+    <t>Valor médio por unidade</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Origem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Quantidade</t>
+    </r>
+  </si>
+  <si>
+    <t>groupby + sum + divisão</t>
+  </si>
+  <si>
+    <t>O valor médio das peças está aumentando?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Como evoluiu o </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>valor médio por kg/unidade de peça</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> ao longo da série histórica, comparando produção nacional e importações?</t>
+    </r>
+  </si>
+  <si>
+    <t>Valor médio por unidade de medida</t>
+  </si>
+  <si>
+    <t>Quais anos tiveram maior movimentação?</t>
+  </si>
+  <si>
+    <t>Quais anos apresentaram os maiores valores e volumes de produção/importação de empilhadeiras e peças?</t>
+  </si>
+  <si>
+    <t>Ranking anual de valor e quantidade</t>
+  </si>
+  <si>
+    <t>groupby + agg + sort_values</t>
+  </si>
+  <si>
+    <t>Houve mudança na origem do mercado ao longo do tempo?</t>
+  </si>
+  <si>
+    <t>A participação da produção nacional e das importações no mercado de empilhadeiras e peças mudou significativamente ao longo da série histórica?</t>
+  </si>
+  <si>
+    <t>Participação (%) por origem e ano</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Origem</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor</t>
+    </r>
+  </si>
+  <si>
+    <t>groupby + sum + transform + divisão</t>
+  </si>
+  <si>
+    <t>Quais categorias movimentam mais dinheiro?</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Ao longo da série histórica, qual foi a participação de </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>empilhadeiras</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> e </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>peças</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> no valor total do mercado?</t>
+    </r>
+  </si>
+  <si>
+    <t>Participação (%) por categoria</t>
+  </si>
+  <si>
+    <r>
+      <t>Ano</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Categoria</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Arial Unicode MS"/>
+      </rPr>
+      <t>Valor</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -185,7 +1743,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -195,6 +1753,18 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -475,19 +2045,497 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2FE2256-985C-4CFD-B0CB-A5244FDAA391}">
+  <dimension ref="A1:F23"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <cols>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="2" width="83.7109375" customWidth="1"/>
+    <col min="3" max="3" width="53.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="43.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.42578125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6">
+      <c r="A1" s="4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>1</v>
+      </c>
+      <c r="D1" s="4" t="s">
+        <v>36</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>3</v>
+      </c>
+      <c r="F1" s="4" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" ht="30">
+      <c r="A2" s="7" t="s">
+        <v>38</v>
+      </c>
+      <c r="B2" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="C2" s="7" t="s">
+        <v>40</v>
+      </c>
+      <c r="D2" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E2" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" ht="30">
+      <c r="A3" s="7" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="C3" s="7" t="s">
+        <v>45</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>46</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" ht="30">
+      <c r="A4" s="7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B4" s="7" t="s">
+        <v>48</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>49</v>
+      </c>
+      <c r="D4" s="6" t="s">
+        <v>50</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" ht="30">
+      <c r="A5" s="7" t="s">
+        <v>51</v>
+      </c>
+      <c r="B5" s="7" t="s">
+        <v>52</v>
+      </c>
+      <c r="C5" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E5" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F5" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" ht="30">
+      <c r="A6" s="7" t="s">
+        <v>55</v>
+      </c>
+      <c r="B6" s="7" t="s">
+        <v>56</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>53</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="E6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="F6" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" ht="30">
+      <c r="A7" s="7" t="s">
+        <v>57</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>58</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>59</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>60</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F7" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6">
+      <c r="A8" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>65</v>
+      </c>
+      <c r="E8" s="6" t="s">
+        <v>61</v>
+      </c>
+      <c r="F8" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" ht="30">
+      <c r="A9" s="7" t="s">
+        <v>66</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>67</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>68</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F9" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" ht="30">
+      <c r="A10" s="7" t="s">
+        <v>71</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>69</v>
+      </c>
+      <c r="E10" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F10" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="30">
+      <c r="A11" s="7" t="s">
+        <v>74</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>75</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D11" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E11" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6">
+      <c r="A12" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>80</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D12" s="6" t="s">
+        <v>77</v>
+      </c>
+      <c r="E12" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" ht="30">
+      <c r="A13" s="7" t="s">
+        <v>81</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E13" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F13" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" ht="30">
+      <c r="A14" s="7" t="s">
+        <v>85</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>86</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>87</v>
+      </c>
+      <c r="D14" s="6" t="s">
+        <v>84</v>
+      </c>
+      <c r="E14" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6">
+      <c r="A15" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>91</v>
+      </c>
+      <c r="E15" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="F15" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" ht="30">
+      <c r="A16" s="7" t="s">
+        <v>92</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>94</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F16" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" ht="30">
+      <c r="A17" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="6" t="s">
+        <v>70</v>
+      </c>
+      <c r="F17" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" ht="30">
+      <c r="A18" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="D18" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E18" s="6" t="s">
+        <v>103</v>
+      </c>
+      <c r="F18" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="30">
+      <c r="A19" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F19" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="30">
+      <c r="A20" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="B20" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>111</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E20" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F20" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="A21" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="B21" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E21" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="22" spans="1:6" ht="30">
+      <c r="A22" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B22" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="C22" s="7" t="s">
+        <v>118</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>119</v>
+      </c>
+      <c r="E22" s="6" t="s">
+        <v>120</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="B23" s="7" t="s">
+        <v>122</v>
+      </c>
+      <c r="C23" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E23" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F23" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E10"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="64" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="39.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="28.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="18.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="48.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="68.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="39.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="33.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="29.28515625" style="1" customWidth="1"/>
+    <col min="6" max="16384" width="8.85546875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:5" ht="15.75" thickBot="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -504,72 +2552,72 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5">
       <c r="A2" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>18</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="E2" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="C2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" s="1" t="s">
+      <c r="B3" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>21</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="1" t="s">
         <v>26</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="C3" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="D3" s="1" t="s">
+      <c r="B4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="E3" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" s="1" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="1" t="s">
+        <v>34</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="C4" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A5" s="1" t="s">
+      <c r="C5" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="D5" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="E5" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="C5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="E5" s="1" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:5">
       <c r="A6" s="1" t="s">
         <v>5</v>
       </c>
@@ -583,10 +2631,10 @@
         <v>7</v>
       </c>
       <c r="E6" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
       <c r="A7" s="1" t="s">
         <v>8</v>
       </c>
@@ -600,10 +2648,10 @@
         <v>7</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
       <c r="A8" s="1" t="s">
         <v>11</v>
       </c>
@@ -617,10 +2665,10 @@
         <v>7</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
       <c r="A9" s="1" t="s">
         <v>15</v>
       </c>
@@ -634,21 +2682,21 @@
         <v>7</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
       <c r="A10" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C10" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="E10" s="1" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
